--- a/교재/엑셀교재v2/010-011_텍스트와_날짜시간함수_실습.xlsx
+++ b/교재/엑셀교재v2/010-011_텍스트와_날짜시간함수_실습.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\엑셀교재v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1D8A4B-E6AA-4A66-A746-32EE2A8AC2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC954ECB-CF98-490F-A26D-87B8464CFF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="375" windowWidth="22200" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24825" yWindow="795" windowWidth="22200" windowHeight="14790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="텍스트_연습" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="55">
   <si>
     <t>010페이지 · 텍스트</t>
   </si>
@@ -56,9 +56,6 @@
     <t>MID</t>
   </si>
   <si>
-    <t>원본 자료: 노트 사진 010페이지</t>
-  </si>
-  <si>
     <t>A   B   C   D</t>
   </si>
   <si>
@@ -135,9 +132,6 @@
   </si>
   <si>
     <t>날짜 만들기</t>
-  </si>
-  <si>
-    <t>원본 자료: 노트 사진 011페이지</t>
   </si>
   <si>
     <t>시간 만들기</t>
@@ -591,19 +585,17 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="27" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="1"/>
@@ -615,11 +607,11 @@
     <row r="6" spans="1:10" ht="27" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="1"/>
@@ -633,7 +625,7 @@
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="1"/>
@@ -647,7 +639,7 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="1"/>
@@ -661,7 +653,7 @@
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="1"/>
@@ -675,7 +667,7 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="1"/>
@@ -699,7 +691,7 @@
     <row r="12" spans="1:10" ht="27" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -737,7 +729,7 @@
     <row r="15" spans="1:10" ht="27" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -751,11 +743,11 @@
     <row r="16" spans="1:10" ht="27" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="1"/>
@@ -767,11 +759,11 @@
     <row r="17" spans="1:10" ht="27" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="1"/>
@@ -785,7 +777,7 @@
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="1"/>
@@ -799,7 +791,7 @@
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="1"/>
@@ -871,7 +863,7 @@
     <row r="25" spans="1:10" ht="27" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -885,7 +877,7 @@
     <row r="26" spans="1:10" ht="27" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -992,13 +984,13 @@
     <row r="2" spans="1:10" ht="27" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="1"/>
@@ -1010,18 +1002,18 @@
     <row r="3" spans="1:10" ht="27" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J3" s="1"/>
     </row>
@@ -1032,19 +1024,19 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="27" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="1"/>
@@ -1052,21 +1044,19 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" ht="27" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="1"/>
@@ -1076,13 +1066,13 @@
     <row r="7" spans="1:10" ht="27" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="1"/>
@@ -1096,7 +1086,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="1"/>
@@ -1106,13 +1096,13 @@
     <row r="9" spans="1:10" ht="27" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1132,10 +1122,10 @@
       <c r="D10" s="7"/>
       <c r="E10" s="1"/>
       <c r="F10" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1160,17 +1150,17 @@
     <row r="12" spans="1:10" ht="27" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1218,7 +1208,7 @@
     <row r="16" spans="1:10" ht="27" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -1235,7 +1225,7 @@
         <v>45144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="1"/>
@@ -1251,7 +1241,7 @@
         <v>45144.611990740741</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="1"/>
@@ -1265,7 +1255,7 @@
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="1"/>
@@ -1278,10 +1268,10 @@
     <row r="20" spans="1:10" ht="27" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="1"/>
@@ -1297,7 +1287,7 @@
         <v>46167</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="1"/>
@@ -1348,7 +1338,7 @@
     <row r="25" spans="1:10" ht="27" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -1362,7 +1352,7 @@
     <row r="26" spans="1:10" ht="27" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -1482,7 +1472,7 @@
     <row r="3" spans="1:10" ht="27" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
@@ -1496,7 +1486,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J3" s="1"/>
     </row>
@@ -1516,19 +1506,17 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="27" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="12" t="str">
         <f>RIGHT(B4,4)</f>
@@ -1543,11 +1531,11 @@
     <row r="6" spans="1:10" ht="27" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" s="12" t="str">
         <f>UPPER(B6)</f>
@@ -1564,7 +1552,7 @@
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="12" t="str">
         <f>LOWER(B3)</f>
@@ -1581,7 +1569,7 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="12" t="str">
         <f>PROPER(B6)</f>
@@ -1598,7 +1586,7 @@
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="12" t="str">
         <f>TRIM(B5)</f>
@@ -1615,7 +1603,7 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" s="12" t="str">
         <f>B4&amp;" 만세"</f>
@@ -1642,7 +1630,7 @@
     <row r="12" spans="1:10" ht="27" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -1680,7 +1668,7 @@
     <row r="15" spans="1:10" ht="27" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -1694,11 +1682,11 @@
     <row r="16" spans="1:10" ht="27" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" s="12" t="str">
         <f>MID(B16,4,4)</f>
@@ -1713,11 +1701,11 @@
     <row r="17" spans="1:10" ht="27" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" s="12" t="str">
         <f>RIGHT(B16,3)</f>
@@ -1734,7 +1722,7 @@
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E18" s="12" t="str">
         <f>PROPER(B17)</f>
@@ -1751,7 +1739,7 @@
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E19" s="12" t="str">
         <f>LEFT(B16,2)&amp;" 지점"</f>
@@ -1826,7 +1814,7 @@
     <row r="25" spans="1:10" ht="27" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -1840,7 +1828,7 @@
     <row r="26" spans="1:10" ht="27" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -1947,16 +1935,16 @@
     <row r="2" spans="1:10" ht="27" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="13">
         <f ca="1">TODAY()</f>
-        <v>46301</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="15">
         <f ca="1">YEAR(C2)</f>
@@ -1964,23 +1952,23 @@
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="27" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="14">
         <f ca="1">NOW()</f>
-        <v>46301.64435949074</v>
+        <v>46307.64158171296</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" s="15">
         <f ca="1">MONTH(C2)</f>
@@ -1988,7 +1976,7 @@
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J3" s="1"/>
     </row>
@@ -1999,50 +1987,48 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" s="15">
         <f ca="1">DAY(C2)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="27" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="13">
         <f ca="1">DATE(G2,G3,G4)</f>
-        <v>46301</v>
+        <v>46307</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" ht="27" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="16">
         <f ca="1">TIME(G6,G7,G8)</f>
-        <v>0.64436342592592588</v>
+        <v>0.64158564814814811</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G6" s="15">
         <f ca="1">HOUR(C3)</f>
@@ -2055,20 +2041,20 @@
     <row r="7" spans="1:10" ht="27" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" s="15">
         <f ca="1">WEEKDAY(C2,2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G7" s="15">
         <f ca="1">MINUTE(C3)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -2081,7 +2067,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G8" s="15">
         <f ca="1">SECOND(C3)</f>
@@ -2094,13 +2080,13 @@
     <row r="9" spans="1:10" ht="27" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2123,10 +2109,10 @@
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -2151,17 +2137,17 @@
     <row r="12" spans="1:10" ht="27" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -2218,7 +2204,7 @@
     <row r="16" spans="1:10" ht="27" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2235,7 +2221,7 @@
         <v>45144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" s="15">
         <f>WEEKDAY(B17,2)</f>
@@ -2254,7 +2240,7 @@
         <v>45144.611990740741</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D18" s="15">
         <f>SECOND(B18)</f>
@@ -2271,7 +2257,7 @@
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D19" s="13">
         <f>WORKDAY(B10,C10,B21)</f>
@@ -2287,10 +2273,10 @@
     <row r="20" spans="1:10" ht="27" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D20" s="13">
         <f>EDATE(B22,1)</f>
@@ -2309,7 +2295,7 @@
         <v>46167</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D21" s="15">
         <f>_xlfn.DAYS(F11,G11)</f>
@@ -2363,7 +2349,7 @@
     <row r="25" spans="1:10" ht="27" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -2377,7 +2363,7 @@
     <row r="26" spans="1:10" ht="27" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>

--- a/교재/엑셀교재v2/010-011_텍스트와_날짜시간함수_실습.xlsx
+++ b/교재/엑셀교재v2/010-011_텍스트와_날짜시간함수_실습.xlsx
@@ -285,7 +285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -303,6 +303,12 @@
     <xf numFmtId="177" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -554,32 +560,40 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="27" customHeight="1">
+    <row r="3" spans="1:10" ht="44" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEFT 함수 사용
+B3의 왼쪽 3글자</t>
+        </is>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="1" t="s">
-        <v>3</v>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노란색 셀에 지정된 함수·연산자로 수식을 입력하세요.</t>
+        </is>
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="27" customHeight="1">
+    <row r="4" spans="1:10" ht="44" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MID 함수 사용
+B3의 4번째부터 2글자</t>
+        </is>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="1"/>
@@ -588,14 +602,17 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="27" customHeight="1">
+    <row r="5" spans="1:10" ht="44" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIGHT 함수 사용
+B4의 오른쪽 4글자</t>
+        </is>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="1"/>
@@ -604,14 +621,17 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="27" customHeight="1">
+    <row r="6" spans="1:10" ht="44" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UPPER 함수 사용
+B6을 대문자로</t>
+        </is>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="1"/>
@@ -620,12 +640,15 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="27" customHeight="1">
+    <row r="7" spans="1:10" ht="44" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOWER 함수 사용
+B3을 소문자로</t>
+        </is>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="1"/>
@@ -634,12 +657,15 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="27" customHeight="1">
+    <row r="8" spans="1:10" ht="44" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROPER 함수 사용
+B6의 첫 글자를 대문자로</t>
+        </is>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="1"/>
@@ -648,12 +674,15 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="27" customHeight="1">
+    <row r="9" spans="1:10" ht="44" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="2" t="s">
-        <v>12</v>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRIM 함수 사용
+B5의 불필요한 공백 제거</t>
+        </is>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="1"/>
@@ -662,12 +691,15 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="27" customHeight="1">
+    <row r="10" spans="1:10" ht="44" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="2" t="s">
-        <v>13</v>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp; 연산자 사용
+B4 뒤에 " 만세" 연결</t>
+        </is>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="1"/>
@@ -740,14 +772,17 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="27" customHeight="1">
+    <row r="16" spans="1:10" ht="44" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="2" t="s">
-        <v>17</v>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MID 함수 사용
+B16에서 연도 4글자</t>
+        </is>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="1"/>
@@ -756,14 +791,17 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="27" customHeight="1">
+    <row r="17" spans="1:10" ht="44" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="2" t="s">
-        <v>19</v>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIGHT 함수 사용
+B16의 끝 3글자</t>
+        </is>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="1"/>
@@ -772,12 +810,15 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="27" customHeight="1">
+    <row r="18" spans="1:10" ht="44" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="2" t="s">
-        <v>20</v>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROPER 함수 사용
+B17의 각 단어 첫 글자 대문자</t>
+        </is>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="1"/>
@@ -786,12 +827,15 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="27" customHeight="1">
+    <row r="19" spans="1:10" ht="44" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="2" t="s">
-        <v>21</v>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEFT 함수와 &amp; 연산자 사용
+B16으로 "서울 지점" 만들기</t>
+        </is>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="1"/>
@@ -981,34 +1025,44 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" ht="27" customHeight="1">
+    <row r="2" spans="1:10" ht="44" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오늘 날짜 (TODAY 함수 사용)</t>
+        </is>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="2" t="s">
-        <v>25</v>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">년 (YEAR 함수 사용)</t>
+        </is>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
-        <v>3</v>
+      <c r="I2" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노란색 셀에 지정된 함수로 수식을 입력하세요.</t>
+        </is>
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="27" customHeight="1">
+    <row r="3" spans="1:10" ht="44" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 날짜·시간 (NOW 함수 사용)</t>
+        </is>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="2" t="s">
-        <v>27</v>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">월 (MONTH 함수 사용)</t>
+        </is>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="1"/>
@@ -1017,14 +1071,16 @@
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="27" customHeight="1">
+    <row r="4" spans="1:10" ht="44" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="2" t="s">
-        <v>29</v>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일 (DAY 함수 사용)</t>
+        </is>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="1"/>
@@ -1033,10 +1089,12 @@
       </c>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="27" customHeight="1">
+    <row r="5" spans="1:10" ht="44" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>31</v>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">날짜 만들기 (DATE 함수 사용)</t>
+        </is>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="1"/>
@@ -1047,53 +1105,64 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="27" customHeight="1">
+    <row r="6" spans="1:10" ht="44" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
-        <v>32</v>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시간 만들기 (TIME 함수 사용)</t>
+        </is>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="2" t="s">
-        <v>33</v>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시 (HOUR 함수 사용)</t>
+        </is>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="27" customHeight="1">
+    <row r="7" spans="1:10" ht="44" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
-        <v>34</v>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요일 번호: 월=1
+(WEEKDAY 함수 사용)</t>
+        </is>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="2" t="s">
-        <v>35</v>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분 (MINUTE 함수 사용)</t>
+        </is>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="27" customHeight="1">
+    <row r="8" spans="1:10" ht="44" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="2" t="s">
-        <v>36</v>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">초 (SECOND 함수 사용)</t>
+        </is>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="27" customHeight="1">
+    <row r="9" spans="1:10" ht="44" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>37</v>
@@ -1101,8 +1170,11 @@
       <c r="C9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>39</v>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료일
+(WORKDAY 함수 사용)</t>
+        </is>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1147,20 +1219,29 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="27" customHeight="1">
+    <row r="12" spans="1:10" ht="44" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>44</v>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3개월 후
+(EDATE 함수 사용)</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3개월 후 말일
+(EOMONTH 함수 사용)</t>
+        </is>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="2" t="s">
-        <v>45</v>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기간: 종료일−시작일
+(DAYS 함수 사용)</t>
+        </is>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1219,13 +1300,16 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="27" customHeight="1">
+    <row r="17" spans="1:10" ht="44" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="6">
         <v>45144</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>47</v>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요일 번호: 월=1
+(WEEKDAY 함수 사용)</t>
+        </is>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="1"/>
@@ -1235,13 +1319,16 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="27" customHeight="1">
+    <row r="18" spans="1:10" ht="44" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="11">
         <v>45144.611990740741</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>48</v>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">초 추출
+(SECOND 함수 사용)</t>
+        </is>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="1"/>
@@ -1251,11 +1338,14 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="27" customHeight="1">
+    <row r="19" spans="1:10" ht="44" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="2" t="s">
-        <v>49</v>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">휴일 포함 완료일
+(WORKDAY 함수 사용)</t>
+        </is>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="1"/>
@@ -1265,13 +1355,16 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="27" customHeight="1">
+    <row r="20" spans="1:10" ht="44" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>51</v>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B22의 1개월 후
+(EDATE 함수 사용)</t>
+        </is>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="1"/>
@@ -1281,13 +1374,16 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="27" customHeight="1">
+    <row r="21" spans="1:10" ht="44" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="6">
         <v>46167</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>52</v>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시작일−종료일
+(DAYS 함수 사용)</t>
+        </is>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="1"/>
@@ -1469,14 +1565,17 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="27" customHeight="1">
+    <row r="3" spans="1:10" ht="44" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEFT 함수 사용
+B3의 왼쪽 3글자</t>
+        </is>
       </c>
       <c r="E3" s="12" t="str">
         <f>LEFT(B3,3)</f>
@@ -1485,19 +1584,24 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="1" t="s">
-        <v>53</v>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노란색 셀에 지정된 함수·연산자로 수식을 입력하세요.</t>
+        </is>
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="27" customHeight="1">
+    <row r="4" spans="1:10" ht="44" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MID 함수 사용
+B3의 4번째부터 2글자</t>
+        </is>
       </c>
       <c r="E4" s="12" t="str">
         <f>MID(B3,4,2)</f>
@@ -1509,14 +1613,17 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="27" customHeight="1">
+    <row r="5" spans="1:10" ht="44" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIGHT 함수 사용
+B4의 오른쪽 4글자</t>
+        </is>
       </c>
       <c r="E5" s="12" t="str">
         <f>RIGHT(B4,4)</f>
@@ -1528,14 +1635,17 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="27" customHeight="1">
+    <row r="6" spans="1:10" ht="44" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UPPER 함수 사용
+B6을 대문자로</t>
+        </is>
       </c>
       <c r="E6" s="12" t="str">
         <f>UPPER(B6)</f>
@@ -1547,12 +1657,15 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="27" customHeight="1">
+    <row r="7" spans="1:10" ht="44" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOWER 함수 사용
+B3을 소문자로</t>
+        </is>
       </c>
       <c r="E7" s="12" t="str">
         <f>LOWER(B3)</f>
@@ -1564,12 +1677,15 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="27" customHeight="1">
+    <row r="8" spans="1:10" ht="44" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROPER 함수 사용
+B6의 첫 글자를 대문자로</t>
+        </is>
       </c>
       <c r="E8" s="12" t="str">
         <f>PROPER(B6)</f>
@@ -1581,12 +1697,15 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="27" customHeight="1">
+    <row r="9" spans="1:10" ht="44" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="2" t="s">
-        <v>12</v>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRIM 함수 사용
+B5의 불필요한 공백 제거</t>
+        </is>
       </c>
       <c r="E9" s="12" t="str">
         <f>TRIM(B5)</f>
@@ -1598,12 +1717,15 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="27" customHeight="1">
+    <row r="10" spans="1:10" ht="44" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="2" t="s">
-        <v>13</v>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp; 연산자 사용
+B4 뒤에 " 만세" 연결</t>
+        </is>
       </c>
       <c r="E10" s="12" t="str">
         <f>B4&amp;" 만세"</f>
@@ -1679,14 +1801,17 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="27" customHeight="1">
+    <row r="16" spans="1:10" ht="44" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="2" t="s">
-        <v>17</v>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MID 함수 사용
+B16에서 연도 4글자</t>
+        </is>
       </c>
       <c r="E16" s="12" t="str">
         <f>MID(B16,4,4)</f>
@@ -1698,14 +1823,17 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="27" customHeight="1">
+    <row r="17" spans="1:10" ht="44" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="2" t="s">
-        <v>19</v>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIGHT 함수 사용
+B16의 끝 3글자</t>
+        </is>
       </c>
       <c r="E17" s="12" t="str">
         <f>RIGHT(B16,3)</f>
@@ -1717,12 +1845,15 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="27" customHeight="1">
+    <row r="18" spans="1:10" ht="44" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="2" t="s">
-        <v>20</v>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROPER 함수 사용
+B17의 각 단어 첫 글자 대문자</t>
+        </is>
       </c>
       <c r="E18" s="12" t="str">
         <f>PROPER(B17)</f>
@@ -1734,12 +1865,15 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="27" customHeight="1">
+    <row r="19" spans="1:10" ht="44" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="2" t="s">
-        <v>21</v>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEFT 함수와 &amp; 연산자 사용
+B16으로 "서울 지점" 만들기</t>
+        </is>
       </c>
       <c r="E19" s="12" t="str">
         <f>LEFT(B16,2)&amp;" 지점"</f>
@@ -1932,10 +2066,12 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" ht="27" customHeight="1">
+    <row r="2" spans="1:10" ht="44" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오늘 날짜 (TODAY 함수 사용)</t>
+        </is>
       </c>
       <c r="C2" s="13">
         <f ca="1">TODAY()</f>
@@ -1943,23 +2079,29 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="2" t="s">
-        <v>25</v>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">년 (YEAR 함수 사용)</t>
+        </is>
       </c>
       <c r="G2" s="15">
         <f ca="1">YEAR(C2)</f>
         <v>2026</v>
       </c>
       <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
-        <v>53</v>
+      <c r="I2" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노란색 셀에 지정된 함수로 수식을 입력하세요.</t>
+        </is>
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="27" customHeight="1">
+    <row r="3" spans="1:10" ht="44" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 날짜·시간 (NOW 함수 사용)</t>
+        </is>
       </c>
       <c r="C3" s="14">
         <f ca="1">NOW()</f>
@@ -1967,8 +2109,10 @@
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="2" t="s">
-        <v>27</v>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">월 (MONTH 함수 사용)</t>
+        </is>
       </c>
       <c r="G3" s="15">
         <f ca="1">MONTH(C2)</f>
@@ -1980,14 +2124,16 @@
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="27" customHeight="1">
+    <row r="4" spans="1:10" ht="44" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="2" t="s">
-        <v>29</v>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일 (DAY 함수 사용)</t>
+        </is>
       </c>
       <c r="G4" s="15">
         <f ca="1">DAY(C2)</f>
@@ -1999,10 +2145,12 @@
       </c>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="27" customHeight="1">
+    <row r="5" spans="1:10" ht="44" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>31</v>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">날짜 만들기 (DATE 함수 사용)</t>
+        </is>
       </c>
       <c r="C5" s="13">
         <f ca="1">DATE(G2,G3,G4)</f>
@@ -2016,10 +2164,12 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="27" customHeight="1">
+    <row r="6" spans="1:10" ht="44" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
-        <v>32</v>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시간 만들기 (TIME 함수 사용)</t>
+        </is>
       </c>
       <c r="C6" s="16">
         <f ca="1">TIME(G6,G7,G8)</f>
@@ -2027,8 +2177,10 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="2" t="s">
-        <v>33</v>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시 (HOUR 함수 사용)</t>
+        </is>
       </c>
       <c r="G6" s="15">
         <f ca="1">HOUR(C3)</f>
@@ -2038,10 +2190,13 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="27" customHeight="1">
+    <row r="7" spans="1:10" ht="44" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
-        <v>34</v>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요일 번호: 월=1
+(WEEKDAY 함수 사용)</t>
+        </is>
       </c>
       <c r="C7" s="15">
         <f ca="1">WEEKDAY(C2,2)</f>
@@ -2049,8 +2204,10 @@
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="2" t="s">
-        <v>35</v>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분 (MINUTE 함수 사용)</t>
+        </is>
       </c>
       <c r="G7" s="15">
         <f ca="1">MINUTE(C3)</f>
@@ -2060,14 +2217,16 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="27" customHeight="1">
+    <row r="8" spans="1:10" ht="44" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="2" t="s">
-        <v>36</v>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">초 (SECOND 함수 사용)</t>
+        </is>
       </c>
       <c r="G8" s="15">
         <f ca="1">SECOND(C3)</f>
@@ -2077,7 +2236,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="27" customHeight="1">
+    <row r="9" spans="1:10" ht="44" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>37</v>
@@ -2085,8 +2244,11 @@
       <c r="C9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>39</v>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료일
+(WORKDAY 함수 사용)</t>
+        </is>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2134,20 +2296,29 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="27" customHeight="1">
+    <row r="12" spans="1:10" ht="44" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>44</v>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3개월 후
+(EDATE 함수 사용)</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3개월 후 말일
+(EOMONTH 함수 사용)</t>
+        </is>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="2" t="s">
-        <v>45</v>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기간: 종료일−시작일
+(DAYS 함수 사용)</t>
+        </is>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -2215,13 +2386,16 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="27" customHeight="1">
+    <row r="17" spans="1:10" ht="44" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="6">
         <v>45144</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>47</v>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요일 번호: 월=1
+(WEEKDAY 함수 사용)</t>
+        </is>
       </c>
       <c r="D17" s="15">
         <f>WEEKDAY(B17,2)</f>
@@ -2234,13 +2408,16 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="27" customHeight="1">
+    <row r="18" spans="1:10" ht="44" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="11">
         <v>45144.611990740741</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>48</v>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">초 추출
+(SECOND 함수 사용)</t>
+        </is>
       </c>
       <c r="D18" s="15">
         <f>SECOND(B18)</f>
@@ -2253,11 +2430,14 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="27" customHeight="1">
+    <row r="19" spans="1:10" ht="44" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="2" t="s">
-        <v>49</v>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">휴일 포함 완료일
+(WORKDAY 함수 사용)</t>
+        </is>
       </c>
       <c r="D19" s="13">
         <f>WORKDAY(B10,C10,B21)</f>
@@ -2270,13 +2450,16 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="27" customHeight="1">
+    <row r="20" spans="1:10" ht="44" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>51</v>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B22의 1개월 후
+(EDATE 함수 사용)</t>
+        </is>
       </c>
       <c r="D20" s="13">
         <f>EDATE(B22,1)</f>
@@ -2289,13 +2472,16 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="27" customHeight="1">
+    <row r="21" spans="1:10" ht="44" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="6">
         <v>46167</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>52</v>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시작일−종료일
+(DAYS 함수 사용)</t>
+        </is>
       </c>
       <c r="D21" s="15">
         <f>_xlfn.DAYS(F11,G11)</f>
